--- a/content/post/drafts/season-prediction/ladies_model-exhaustive-tests-actual_rmse.xlsx
+++ b/content/post/drafts/season-prediction/ladies_model-exhaustive-tests-actual_rmse.xlsx
@@ -41,13 +41,13 @@
     <t xml:space="preserve">Linear</t>
   </si>
   <si>
+    <t xml:space="preserve">Random Forest</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAM</t>
   </si>
   <si>
     <t xml:space="preserve">Polynomial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Forest</t>
   </si>
   <si>
     <t xml:space="preserve">KNN</t>
@@ -457,25 +457,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.151671355976105</v>
+        <v>0.148783236708454</v>
       </c>
       <c r="C3" t="n">
-        <v>0.160698567717755</v>
+        <v>0.149701037050461</v>
       </c>
       <c r="D3" t="n">
-        <v>0.237735343933206</v>
+        <v>0.231140419508574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.243733171850453</v>
+        <v>0.258831225058256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.128189779905783</v>
+        <v>0.126542218240768</v>
       </c>
       <c r="G3" t="n">
-        <v>0.130677932637298</v>
+        <v>0.135056333816884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.175451025336767</v>
+        <v>0.175009078397233</v>
       </c>
     </row>
     <row r="4">
@@ -483,25 +483,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.132277729312734</v>
+        <v>0.151671355976105</v>
       </c>
       <c r="C4" t="n">
-        <v>0.144407144914989</v>
+        <v>0.160698567717755</v>
       </c>
       <c r="D4" t="n">
-        <v>0.236739511434969</v>
+        <v>0.237735343933206</v>
       </c>
       <c r="E4" t="n">
-        <v>0.254136340769532</v>
+        <v>0.243733171850453</v>
       </c>
       <c r="F4" t="n">
-        <v>0.148367372812526</v>
+        <v>0.128189779905783</v>
       </c>
       <c r="G4" t="n">
-        <v>0.137141837583835</v>
+        <v>0.130677932637298</v>
       </c>
       <c r="H4" t="n">
-        <v>0.175511656138098</v>
+        <v>0.175451025336767</v>
       </c>
     </row>
     <row r="5">
@@ -509,25 +509,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.148616348382184</v>
+        <v>0.132277729312734</v>
       </c>
       <c r="C5" t="n">
-        <v>0.151050473386199</v>
+        <v>0.144407144914989</v>
       </c>
       <c r="D5" t="n">
-        <v>0.23160535918417</v>
+        <v>0.236739511434969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.258546724542533</v>
+        <v>0.254136340769532</v>
       </c>
       <c r="F5" t="n">
-        <v>0.130106485686569</v>
+        <v>0.148367372812526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.135134546199673</v>
+        <v>0.137141837583835</v>
       </c>
       <c r="H5" t="n">
-        <v>0.175843322896888</v>
+        <v>0.175511656138098</v>
       </c>
     </row>
     <row r="6">
